--- a/survey_templates/042_greenhouse_grower_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/042_greenhouse_grower_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Operator Suggestions Areas Other</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Operator Suggestions Actions Areas Other</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Operator Suggestions Implementation Status Other</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Follow Up Areas Other</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1233,46 +1233,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>operations_satisfaction_choices</t>
+          <t>satisfaction_areas_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>greenhouse_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Greenhouse management</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>operations_satisfaction_choices</t>
+          <t>satisfaction_areas_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>crop_management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Crop management</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>greenhouse_management</t>
+          <t>pest_management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greenhouse management</t>
+          <t>Pest management</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>crop_management</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Crop management</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1318,46 +1318,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pest_management</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pest management</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>satisfaction_areas_choices</t>
+          <t>operator_suggestions_areas_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>greenhouse_operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Greenhouse operations</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>satisfaction_areas_choices</t>
+          <t>operator_suggestions_areas_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>greenhouse_operations</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greenhouse operations</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1386,46 +1386,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>operator_suggestions_areas_choices</t>
+          <t>operator_suggestions_actions_areas_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>improve_services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Improve services</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>operator_suggestions_areas_choices</t>
+          <t>operator_suggestions_actions_areas_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>improve_communication</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Improve communication</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>improve_services</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Improve services</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1454,46 +1454,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>improve_communication</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Improve communication</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>operator_suggestions_actions_areas_choices</t>
+          <t>operator_suggestions_implementation_status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>implemented</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>operator_suggestions_actions_areas_choices</t>
+          <t>operator_suggestions_implementation_status_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_yet_implemented</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not yet implemented</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>implemented</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
@@ -1522,46 +1522,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>not_yet_implemented</t>
+          <t>no_plans</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Not yet implemented</t>
+          <t>No plans</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>operator_suggestions_implementation_status_choices</t>
+          <t>follow_up_areas_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>greenhouse_operations</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Greenhouse operations</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>operator_suggestions_implementation_status_choices</t>
+          <t>follow_up_areas_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no_plans</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No plans</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>greenhouse_operations</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greenhouse operations</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1590,46 +1590,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>follow_up_areas_choices</t>
+          <t>follow_up_next_steps_areas_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>improve_services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Improve services</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>follow_up_areas_choices</t>
+          <t>follow_up_next_steps_areas_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>improve_communication</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Improve communication</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>improve_services</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Improve services</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1658,44 +1658,10 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>improve_communication</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
-        <is>
-          <t>Improve communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>follow_up_next_steps_areas_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>other_(please_specify)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Other (please specify)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>follow_up_next_steps_areas_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
         <is>
           <t>None</t>
         </is>
